--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.73742188899907</v>
+        <v>9.057331056962349</v>
       </c>
       <c r="D2" t="n">
-        <v>56.80645350022948</v>
+        <v>9.23104869378729</v>
       </c>
       <c r="E2" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F2" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.08175272262278</v>
+        <v>8.950784817426202</v>
       </c>
       <c r="D3" t="n">
-        <v>56.14275109259719</v>
+        <v>9.123197052547043</v>
       </c>
       <c r="E3" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F3" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.75902362605991</v>
+        <v>9.710841339234735</v>
       </c>
       <c r="D4" t="n">
-        <v>60.65496210690503</v>
+        <v>9.856431342372067</v>
       </c>
       <c r="E4" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.86240857138385</v>
+        <v>7.127641392849875</v>
       </c>
       <c r="D5" t="n">
-        <v>44.86862558342462</v>
+        <v>7.2911516573065</v>
       </c>
       <c r="E5" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F5" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.57722879676493</v>
+        <v>7.406299679474301</v>
       </c>
       <c r="D6" t="n">
-        <v>45.37490037339521</v>
+        <v>7.373421310676721</v>
       </c>
       <c r="E6" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F6" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.37240266778184</v>
+        <v>4.610515433514549</v>
       </c>
       <c r="D7" t="n">
-        <v>27.71774707744019</v>
+        <v>4.504133900084032</v>
       </c>
       <c r="E7" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F7" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.23412466101811</v>
+        <v>7.350545257415443</v>
       </c>
       <c r="D8" t="n">
-        <v>44.99826782574306</v>
+        <v>7.312218521683246</v>
       </c>
       <c r="E8" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F8" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.64347236087186</v>
+        <v>7.742064258641678</v>
       </c>
       <c r="D9" t="n">
-        <v>46.85198579763385</v>
+        <v>7.613447692115501</v>
       </c>
       <c r="E9" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F9" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.63273332197931</v>
+        <v>6.115319164821638</v>
       </c>
       <c r="D10" t="n">
-        <v>36.61507650873168</v>
+        <v>5.949949932668899</v>
       </c>
       <c r="E10" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F10" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>59.79495825437285</v>
+        <v>9.716680716335588</v>
       </c>
       <c r="D11" t="n">
-        <v>58.80183069372331</v>
+        <v>9.555297487730039</v>
       </c>
       <c r="E11" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F11" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>60.7219845665751</v>
+        <v>9.867322492068453</v>
       </c>
       <c r="D12" t="n">
-        <v>59.66134380043498</v>
+        <v>9.694968367570686</v>
       </c>
       <c r="E12" t="n">
-        <v>9.820674270538545</v>
+        <v>1.595859568962513</v>
       </c>
       <c r="F12" t="n">
-        <v>10.06647294565189</v>
+        <v>1.635801853668433</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
